--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ44"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91069</v>
+        <v>91071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92101</v>
+        <v>92103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3906,48 +3906,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135826990</v>
+        <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>98142</v>
+        <v>58084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Haikamyren, Lu lm</t>
+          <t>Pakko, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>711383</v>
+        <v>711519</v>
       </c>
       <c r="R30" t="n">
-        <v>7419621</v>
+        <v>7419470</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3971,22 +3979,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Fyra nyfikna fåglar kom på besök under fikarasten i  skogen.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4001,27 +4014,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135826990</t>
+          <t>https://artportalen.se/Sighting/135916593</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135832011</v>
+        <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4049,17 +4062,17 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pakko, Lu lm</t>
+          <t>Haikamyren, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>711055</v>
+        <v>711383</v>
       </c>
       <c r="R31" t="n">
-        <v>7419913</v>
+        <v>7419621</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4088,7 +4101,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4098,7 +4111,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,27 +4126,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832011</t>
+          <t>https://artportalen.se/Sighting/135826990</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135832026</v>
+        <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4165,13 +4178,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>711499</v>
+        <v>711055</v>
       </c>
       <c r="R32" t="n">
-        <v>7419544</v>
+        <v>7419913</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4200,7 +4213,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4210,7 +4223,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,54 +4249,54 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832026</t>
+          <t>https://artportalen.se/Sighting/135832011</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135826986</v>
+        <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>79199</v>
+        <v>98144</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Haikamyren, Lu lm</t>
+          <t>Pakko, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>711530</v>
+        <v>711499</v>
       </c>
       <c r="R33" t="n">
-        <v>7419462</v>
+        <v>7419544</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4312,7 +4325,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4322,7 +4335,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4337,24 +4350,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135826986</t>
+          <t>https://artportalen.se/Sighting/135832026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135826988</v>
+        <v>135826986</v>
       </c>
       <c r="B34" t="n">
         <v>79199</v>
@@ -4389,10 +4402,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>711519</v>
+        <v>711530</v>
       </c>
       <c r="R34" t="n">
-        <v>7419478</v>
+        <v>7419462</v>
       </c>
       <c r="S34" t="n">
         <v>9</v>
@@ -4424,7 +4437,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4434,7 +4447,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4460,13 +4473,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135826988</t>
+          <t>https://artportalen.se/Sighting/135826986</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135827012</v>
+        <v>135826988</v>
       </c>
       <c r="B35" t="n">
         <v>79199</v>
@@ -4501,13 +4514,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>711549</v>
+        <v>711519</v>
       </c>
       <c r="R35" t="n">
-        <v>7419622</v>
+        <v>7419478</v>
       </c>
       <c r="S35" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4536,7 +4549,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4546,7 +4559,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4572,13 +4585,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827012</t>
+          <t>https://artportalen.se/Sighting/135826988</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135832006</v>
+        <v>135827012</v>
       </c>
       <c r="B36" t="n">
         <v>79199</v>
@@ -4609,17 +4622,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Pakko, Lu lm</t>
+          <t>Haikamyren, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>711246</v>
+        <v>711549</v>
       </c>
       <c r="R36" t="n">
-        <v>7419696</v>
+        <v>7419622</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4648,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4658,7 +4671,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4673,27 +4686,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832006</t>
+          <t>https://artportalen.se/Sighting/135827012</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135826995</v>
+        <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>80031</v>
+        <v>79199</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,37 +4714,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Haikamyren, Lu lm</t>
+          <t>Pakko, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>711255</v>
+        <v>711246</v>
       </c>
       <c r="R37" t="n">
-        <v>7419615</v>
+        <v>7419696</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4760,7 +4773,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4770,7 +4783,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4785,24 +4798,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135826995</t>
+          <t>https://artportalen.se/Sighting/135832006</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135827014</v>
+        <v>135826995</v>
       </c>
       <c r="B38" t="n">
         <v>80031</v>
@@ -4837,13 +4850,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>711389</v>
+        <v>711255</v>
       </c>
       <c r="R38" t="n">
-        <v>7419528</v>
+        <v>7419615</v>
       </c>
       <c r="S38" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4872,7 +4885,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4882,7 +4895,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,13 +4921,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827014</t>
+          <t>https://artportalen.se/Sighting/135826995</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135832002</v>
+        <v>135827014</v>
       </c>
       <c r="B39" t="n">
         <v>80031</v>
@@ -4945,17 +4958,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Pakko, Lu lm</t>
+          <t>Haikamyren, Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>711293</v>
+        <v>711389</v>
       </c>
       <c r="R39" t="n">
-        <v>7419689</v>
+        <v>7419528</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4984,7 +4997,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4994,7 +5007,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,24 +5022,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832002</t>
+          <t>https://artportalen.se/Sighting/135827014</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135832008</v>
+        <v>135832002</v>
       </c>
       <c r="B40" t="n">
         <v>80031</v>
@@ -5061,13 +5074,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>711144</v>
+        <v>711293</v>
       </c>
       <c r="R40" t="n">
-        <v>7419769</v>
+        <v>7419689</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5096,7 +5109,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5106,7 +5119,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,13 +5145,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832008</t>
+          <t>https://artportalen.se/Sighting/135832002</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135832012</v>
+        <v>135832008</v>
       </c>
       <c r="B41" t="n">
         <v>80031</v>
@@ -5173,10 +5186,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>711213</v>
+        <v>711144</v>
       </c>
       <c r="R41" t="n">
-        <v>7419965</v>
+        <v>7419769</v>
       </c>
       <c r="S41" t="n">
         <v>6</v>
@@ -5208,7 +5221,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5218,7 +5231,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5244,16 +5257,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832012</t>
+          <t>https://artportalen.se/Sighting/135832008</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135826989</v>
+        <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>79464</v>
+        <v>80031</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5261,37 +5274,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Haikamyren, Lu lm</t>
+          <t>Pakko, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>711506</v>
+        <v>711213</v>
       </c>
       <c r="R42" t="n">
-        <v>7419497</v>
+        <v>7419965</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5320,7 +5333,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5330,7 +5343,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5345,24 +5358,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Marie Persson</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135826989</t>
+          <t>https://artportalen.se/Sighting/135832012</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135832000</v>
+        <v>135826989</v>
       </c>
       <c r="B43" t="n">
         <v>79464</v>
@@ -5393,17 +5406,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Pakko, Lu lm</t>
+          <t>Haikamyren, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>711426</v>
+        <v>711506</v>
       </c>
       <c r="R43" t="n">
-        <v>7419602</v>
+        <v>7419497</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5432,7 +5445,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5442,7 +5455,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5457,24 +5470,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Elin Kannerby, Marie Persson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135832000</t>
+          <t>https://artportalen.se/Sighting/135826989</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135832028</v>
+        <v>135832000</v>
       </c>
       <c r="B44" t="n">
         <v>79464</v>
@@ -5509,13 +5522,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>711403</v>
+        <v>711426</v>
       </c>
       <c r="R44" t="n">
-        <v>7419528</v>
+        <v>7419602</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5544,7 +5557,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5554,7 +5567,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5579,6 +5592,118 @@
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135832000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135832028</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pakko, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>711403</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7419528</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135832028</t>
         </is>
@@ -5629,6 +5754,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135826999</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135827001</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92296</v>
+        <v>92310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91071</v>
+        <v>91073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92103</v>
+        <v>92117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92446</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135826997</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135827016</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135827017</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135827018</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135827019</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135827020</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135827021</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91073</v>
+        <v>91074</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91074</v>
+        <v>91075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135826999</v>
       </c>
       <c r="B2" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135827001</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92462</v>
+        <v>92463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78847</v>
+        <v>78848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135826997</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135827016</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135827017</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135827018</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135827019</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135827020</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135827021</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135826999</v>
       </c>
       <c r="B2" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135827001</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91076</v>
+        <v>91082</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92463</v>
+        <v>92469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78848</v>
+        <v>78852</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135826997</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135827016</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135827017</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135827018</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135827019</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135827020</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135827021</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135826999</v>
       </c>
       <c r="B2" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135827001</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91082</v>
+        <v>91083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92469</v>
+        <v>92470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135826997</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135827016</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135827017</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135827018</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135827019</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135827020</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135827021</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92470</v>
+        <v>92476</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78853</v>
+        <v>78857</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135826999</v>
       </c>
       <c r="B2" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135827001</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92476</v>
+        <v>92483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78857</v>
+        <v>78863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135826997</v>
       </c>
       <c r="B23" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135827016</v>
       </c>
       <c r="B24" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135827017</v>
       </c>
       <c r="B25" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135827018</v>
       </c>
       <c r="B26" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135827019</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135827020</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135827021</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>58092</v>
+        <v>58097</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92483</v>
+        <v>92484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 61760-2024 artfynd.xlsx
+++ b/artfynd/A 61760-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135826999</v>
       </c>
       <c r="B2" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135827001</v>
       </c>
       <c r="B3" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135831997</v>
       </c>
       <c r="B4" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>135832001</v>
       </c>
       <c r="B5" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135826985</v>
       </c>
       <c r="B6" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135826992</v>
       </c>
       <c r="B7" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>135832032</v>
       </c>
       <c r="B8" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>135831999</v>
       </c>
       <c r="B9" t="n">
-        <v>92484</v>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>135826994</v>
       </c>
       <c r="B10" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>135832010</v>
       </c>
       <c r="B11" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>135832024</v>
       </c>
       <c r="B12" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>135832027</v>
       </c>
       <c r="B13" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>135832030</v>
       </c>
       <c r="B14" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>135826996</v>
       </c>
       <c r="B15" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>135827013</v>
       </c>
       <c r="B16" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135831996</v>
       </c>
       <c r="B17" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>135832007</v>
       </c>
       <c r="B18" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>135832029</v>
       </c>
       <c r="B19" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>135826984</v>
       </c>
       <c r="B20" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>135826987</v>
       </c>
       <c r="B21" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>135826993</v>
       </c>
       <c r="B22" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>135826997</v>
       </c>
       <c r="B23" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135827016</v>
       </c>
       <c r="B24" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>135827017</v>
       </c>
       <c r="B25" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>135827018</v>
       </c>
       <c r="B26" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>135827019</v>
       </c>
       <c r="B27" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>135827020</v>
       </c>
       <c r="B28" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>135827021</v>
       </c>
       <c r="B29" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>135916593</v>
       </c>
       <c r="B30" t="n">
-        <v>58097</v>
+        <v>58110</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>135826990</v>
       </c>
       <c r="B31" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>135832011</v>
       </c>
       <c r="B32" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>135832026</v>
       </c>
       <c r="B33" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>135826986</v>
       </c>
       <c r="B34" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>135826988</v>
       </c>
       <c r="B35" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>135827012</v>
       </c>
       <c r="B36" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>135832006</v>
       </c>
       <c r="B37" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>135826995</v>
       </c>
       <c r="B38" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>135827014</v>
       </c>
       <c r="B39" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>135832002</v>
       </c>
       <c r="B40" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>135832008</v>
       </c>
       <c r="B41" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>135832012</v>
       </c>
       <c r="B42" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>135826989</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>135832000</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>135832028</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
